--- a/SubRes_Tmpl/SubRES_H2-Production.xlsx
+++ b/SubRes_Tmpl/SubRES_H2-Production.xlsx
@@ -1346,17 +1346,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
+      <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="1"/>
@@ -1367,8 +1362,13 @@
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="51">
+  <fills count="49">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1551,12 +1551,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1654,12 +1648,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2124,64 +2112,64 @@
     <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -8246,8 +8234,6 @@
       <c r="AV16" s="10">
         <v>3000</v>
       </c>
-      <c r="AW16"/>
-      <c r="AX16"/>
       <c r="BA16" s="10">
         <v>10</v>
       </c>
@@ -8290,7 +8276,8 @@
       <c r="AM17" s="9"/>
       <c r="AN17"/>
       <c r="AO17" s="9">
-        <v>1</v>
+        <f>1/AL16</f>
+        <v>1.11111111111111</v>
       </c>
       <c r="AQ17"/>
       <c r="AR17"/>
@@ -8392,8 +8379,6 @@
       <c r="AV19" s="10">
         <v>3500</v>
       </c>
-      <c r="AW19"/>
-      <c r="AX19"/>
       <c r="BA19" s="10">
         <v>12</v>
       </c>
@@ -8408,7 +8393,8 @@
       </c>
       <c r="AM20" s="9"/>
       <c r="AO20" s="9">
-        <v>1</v>
+        <f>1/AL19</f>
+        <v>1.08695652173913</v>
       </c>
     </row>
     <row r="21" spans="2:68">
@@ -8456,8 +8442,6 @@
       <c r="AV22" s="10">
         <v>4000</v>
       </c>
-      <c r="AW22"/>
-      <c r="AX22"/>
       <c r="BA22" s="10">
         <v>13</v>
       </c>
@@ -8486,7 +8470,8 @@
       <c r="AL23" s="10"/>
       <c r="AM23" s="9"/>
       <c r="AO23" s="9">
-        <v>1</v>
+        <f>1/AL22</f>
+        <v>1.08695652173913</v>
       </c>
     </row>
     <row r="24" spans="2:68">
@@ -8579,8 +8564,6 @@
       <c r="AV25" s="10">
         <v>4000</v>
       </c>
-      <c r="AW25"/>
-      <c r="AX25"/>
       <c r="BA25" s="10">
         <v>13</v>
       </c>
@@ -8612,7 +8595,8 @@
       <c r="AL26" s="10"/>
       <c r="AM26" s="9"/>
       <c r="AO26" s="9">
-        <v>1</v>
+        <f>1/AL25</f>
+        <v>1.08695652173913</v>
       </c>
     </row>
     <row r="27" spans="2:68">
@@ -8664,8 +8648,6 @@
       <c r="AV28" s="10">
         <v>4000</v>
       </c>
-      <c r="AW28"/>
-      <c r="AX28"/>
       <c r="BA28" s="10">
         <v>13</v>
       </c>
@@ -8688,7 +8670,8 @@
       <c r="AL29" s="10"/>
       <c r="AM29" s="9"/>
       <c r="AO29" s="9">
-        <v>1</v>
+        <f>1/AL28</f>
+        <v>1.08695652173913</v>
       </c>
     </row>
     <row r="30" spans="2:68">
@@ -8750,8 +8733,6 @@
       <c r="AV31" s="10">
         <v>4000</v>
       </c>
-      <c r="AW31"/>
-      <c r="AX31"/>
       <c r="BA31" s="10">
         <v>13</v>
       </c>
@@ -8778,7 +8759,8 @@
       </c>
       <c r="AM32" s="9"/>
       <c r="AO32" s="9">
-        <v>1</v>
+        <f>1/AL31</f>
+        <v>1.08695652173913</v>
       </c>
     </row>
     <row r="33" spans="2:51">
@@ -8879,8 +8861,9 @@
       <c r="AK35" t="s">
         <v>212</v>
       </c>
-      <c r="AO35">
-        <v>1</v>
+      <c r="AO35" s="9">
+        <f>1/AL34</f>
+        <v>1.25</v>
       </c>
     </row>
     <row r="36" ht="16" spans="2:51">
